--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 13,07,26 лгрсч ост зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 13,07,26 лгрсч ост зпф.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F618787-D4E9-45EF-A32C-9EA62C9D9882}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D62E2A4-2863-4322-9E7A-736AC595DC46}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -148,6 +145,12 @@
   </si>
   <si>
     <t>матрица</t>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>20,07,</t>
   </si>
 </sst>
 </file>
@@ -736,25 +739,25 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
@@ -799,19 +802,21 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
-      <c r="Q4" s="1"/>
+      <c r="Q4" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
@@ -885,7 +890,7 @@
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -900,7 +905,7 @@
       <c r="V5" s="1"/>
       <c r="W5" s="4">
         <f>SUM(W6:W500)</f>
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
@@ -931,10 +936,10 @@
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -945,7 +950,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
@@ -1013,10 +1018,10 @@
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1">
         <v>157.28800000000001</v>
@@ -1033,7 +1038,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1066,7 +1071,7 @@
         <v>6.3423999999999996</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W7" s="1">
         <f t="shared" si="2"/>
@@ -1101,10 +1106,10 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1">
         <v>306</v>
@@ -1119,7 +1124,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1150,7 +1155,7 @@
         <v>0.9</v>
       </c>
       <c r="V8" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W8" s="1">
         <f t="shared" si="2"/>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -1199,7 +1204,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1">
@@ -1267,10 +1272,10 @@
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1">
         <v>85</v>
@@ -1287,7 +1292,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -1355,10 +1360,10 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1">
         <v>257</v>
@@ -1375,7 +1380,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1395,12 +1400,11 @@
         <v>24.2</v>
       </c>
       <c r="Q11" s="5">
-        <f t="shared" ref="Q11:Q12" si="6">15*P11-O11-F11</f>
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>15.12396694214876</v>
       </c>
       <c r="S11" s="1">
         <f t="shared" si="5"/>
@@ -1415,7 +1419,7 @@
       <c r="V11" s="1"/>
       <c r="W11" s="1">
         <f t="shared" si="2"/>
-        <v>41.1</v>
+        <v>42</v>
       </c>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
@@ -1446,10 +1450,10 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1">
         <v>198</v>
@@ -1466,7 +1470,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1486,12 +1490,11 @@
         <v>19</v>
       </c>
       <c r="Q12" s="5">
-        <f t="shared" si="6"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R12" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14.894736842105264</v>
       </c>
       <c r="S12" s="1">
         <f t="shared" si="5"/>
@@ -1506,7 +1509,7 @@
       <c r="V12" s="1"/>
       <c r="W12" s="1">
         <f t="shared" si="2"/>
-        <v>7.6999999999999993</v>
+        <v>7</v>
       </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
@@ -1537,10 +1540,10 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="1">
         <v>84</v>
@@ -1557,7 +1560,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1625,10 +1628,10 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="1">
         <v>265</v>
@@ -1645,7 +1648,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -1678,7 +1681,7 @@
         <v>14.4</v>
       </c>
       <c r="V14" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W14" s="1">
         <f t="shared" si="2"/>
@@ -1713,10 +1716,10 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -1727,7 +1730,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
@@ -1795,10 +1798,10 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" s="1">
         <v>35</v>
@@ -1813,7 +1816,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -1848,7 +1851,7 @@
         <v>26.4</v>
       </c>
       <c r="V16" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" si="2"/>
